--- a/data/trans_camb/P44-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P44-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 10,12</t>
+          <t>0,45; 9,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 30,27</t>
+          <t>19,82; 30,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 7,32</t>
+          <t>-0,8; 7,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 26,25</t>
+          <t>18,03; 26,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,31</t>
+          <t>1,09; 7,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,1; 27,09</t>
+          <t>20,41; 26,93</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 264,29</t>
+          <t>4,48; 241,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>230,58; 840,2</t>
+          <t>221,69; 818,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 191,67</t>
+          <t>-12,91; 189,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215,3; 729,21</t>
+          <t>220,93; 790,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,8; 173,44</t>
+          <t>10,28; 173,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>270,12; 693,69</t>
+          <t>277,83; 668,7</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,45</t>
+          <t>-3,55; 5,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,89; 78,1</t>
+          <t>25,46; 77,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 1,85</t>
+          <t>-6,31; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 24,54</t>
+          <t>15,6; 24,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,65</t>
+          <t>-3,41; 2,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,3; 62,94</t>
+          <t>22,5; 63,16</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 86,97</t>
+          <t>-30,81; 95,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281,87; 1745,37</t>
+          <t>274,7; 1479,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,21; 27,98</t>
+          <t>-54,25; 26,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126,93; 363,35</t>
+          <t>129,02; 360,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 36,31</t>
+          <t>-32,07; 33,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>230,2; 846,75</t>
+          <t>231,02; 939,09</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 5,61</t>
+          <t>-6,32; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,22; 28,32</t>
+          <t>14,69; 28,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,39</t>
+          <t>-6,92; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 16,98</t>
+          <t>-7,27; 17,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,55</t>
+          <t>-4,97; 2,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 20,36</t>
+          <t>-0,1; 20,04</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 68,87</t>
+          <t>-41,1; 69,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,28; 340,3</t>
+          <t>85,32; 362,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 36,34</t>
+          <t>-61,03; 32,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 207,41</t>
+          <t>-54,76; 210,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,5; 30,34</t>
+          <t>-39,82; 33,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 220,86</t>
+          <t>1,07; 220,34</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 7,53</t>
+          <t>-2,85; 7,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,4; 37,09</t>
+          <t>25,67; 36,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,0</t>
+          <t>-2,25; 4,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,59; 32,2</t>
+          <t>24,14; 32,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,92</t>
+          <t>-1,07; 5,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,65; 33,12</t>
+          <t>26,31; 33,18</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 85,84</t>
+          <t>-19,39; 83,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>168,5; 418,48</t>
+          <t>160,67; 423,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 106,67</t>
+          <t>-30,62; 102,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>289,8; 751,41</t>
+          <t>285,55; 755,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 73,21</t>
+          <t>-10,84; 73,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>241,9; 481,07</t>
+          <t>244,77; 481,33</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,69</t>
+          <t>-0,21; 4,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,39; 56,99</t>
+          <t>25,9; 55,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,8</t>
+          <t>-1,97; 1,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,15; 23,23</t>
+          <t>9,33; 22,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,54</t>
+          <t>-0,6; 2,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,08; 40,55</t>
+          <t>20,61; 40,95</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 57,89</t>
+          <t>-2,49; 56,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>260,36; 647,21</t>
+          <t>252,2; 661,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 27,72</t>
+          <t>-23,62; 29,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137,19; 336,2</t>
+          <t>140,99; 342,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 34,17</t>
+          <t>-5,74; 36,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>234,27; 487,57</t>
+          <t>233,98; 505,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P44-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P44-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>25,28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,39</t>
+          <t>22,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,73</t>
+          <t>23,94</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 9,69</t>
+          <t>0,73; 9,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 30,44</t>
+          <t>20,05; 30,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,16</t>
+          <t>-0,85; 7,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,03; 26,55</t>
+          <t>18,77; 26,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,38</t>
+          <t>1,02; 7,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,93</t>
+          <t>20,46; 27,0</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>444,56%</t>
+          <t>444,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>411,5%</t>
+          <t>418,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>426,86%</t>
+          <t>430,57%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 241,24</t>
+          <t>8,09; 292,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>221,69; 818,47</t>
+          <t>242,36; 818,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 189,42</t>
+          <t>-19,86; 194,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220,93; 790,05</t>
+          <t>214,28; 690,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 173,98</t>
+          <t>13,41; 169,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>277,83; 668,7</t>
+          <t>285,03; 671,59</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51,56</t>
+          <t>27,12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,23</t>
+          <t>20,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,91</t>
+          <t>23,52</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 5,69</t>
+          <t>-3,32; 6,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,46; 77,29</t>
+          <t>21,92; 32,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,88</t>
+          <t>-5,9; 2,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,57</t>
+          <t>15,9; 24,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,48</t>
+          <t>-3,44; 2,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,5; 63,16</t>
+          <t>19,81; 26,78</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>599,95%</t>
+          <t>315,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214,16%</t>
+          <t>214,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>429,57%</t>
+          <t>259,62%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 95,02</t>
+          <t>-30,0; 102,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>274,7; 1479,11</t>
+          <t>185,03; 540,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 26,73</t>
+          <t>-50,4; 36,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129,02; 360,5</t>
+          <t>128,24; 348,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 33,65</t>
+          <t>-33,07; 32,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>231,02; 939,09</t>
+          <t>172,47; 362,62</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21,75</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>16,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>18,82</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,72</t>
+          <t>-6,81; 5,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,69; 28,46</t>
+          <t>14,21; 27,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 2,0</t>
+          <t>-7,02; 2,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 17,02</t>
+          <t>10,81; 21,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,62</t>
+          <t>-4,85; 2,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 20,04</t>
+          <t>14,33; 22,97</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>186,24%</t>
+          <t>178,99%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>178,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>114,14%</t>
+          <t>184,16%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 69,36</t>
+          <t>-43,82; 71,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,32; 362,77</t>
+          <t>88,41; 351,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 32,8</t>
+          <t>-58,47; 42,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 210,68</t>
+          <t>87,16; 332,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 33,34</t>
+          <t>-39,33; 35,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 220,34</t>
+          <t>109,74; 285,86</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31,55</t>
+          <t>31,01</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,33</t>
+          <t>28,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,97</t>
+          <t>30,02</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 7,46</t>
+          <t>-2,36; 7,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,67; 36,91</t>
+          <t>25,65; 36,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,13</t>
+          <t>-2,27; 4,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,14; 32,29</t>
+          <t>24,88; 32,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,01</t>
+          <t>-0,99; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,31; 33,18</t>
+          <t>26,43; 33,34</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>266,74%</t>
+          <t>262,12%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>458,7%</t>
+          <t>468,58%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>348,75%</t>
+          <t>349,36%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 83,11</t>
+          <t>-16,81; 88,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>160,67; 423,97</t>
+          <t>174,79; 428,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 102,77</t>
+          <t>-30,25; 110,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>285,55; 755,41</t>
+          <t>287,1; 744,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 73,93</t>
+          <t>-9,08; 69,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>244,77; 481,33</t>
+          <t>241,91; 475,79</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36,12</t>
+          <t>26,58</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19,02</t>
+          <t>22,76</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>24,63</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,71</t>
+          <t>-0,38; 4,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,9; 55,91</t>
+          <t>23,7; 29,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,96</t>
+          <t>-2,1; 1,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,33; 22,98</t>
+          <t>20,62; 25,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,69</t>
+          <t>-0,63; 2,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,61; 40,95</t>
+          <t>22,86; 26,44</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>379,09%</t>
+          <t>278,95%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>253,56%</t>
+          <t>303,47%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>325,88%</t>
+          <t>292,94%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 56,63</t>
+          <t>-4,16; 58,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>252,2; 661,52</t>
+          <t>207,12; 366,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 29,74</t>
+          <t>-25,54; 29,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140,99; 342,01</t>
+          <t>231,93; 400,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 36,06</t>
+          <t>-6,98; 34,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>233,98; 505,67</t>
+          <t>239,76; 354,41</t>
         </is>
       </c>
     </row>
